--- a/data/trans_orig/P57C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha sido optimista respecto a su futuro en 2023</t>
+          <t>Población según si ha sido optimista respecto a su futuro en 2023 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>19075</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38693</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35067</t>
+          <t>34353</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52640</t>
+          <t>52518</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57412</t>
+          <t>58485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85354</t>
+          <t>86342</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>48494</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73604</t>
+          <t>74479</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100995</t>
+          <t>100529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>130481</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157407</t>
+          <t>154743</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197014</t>
+          <t>195147</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>94911</t>
+          <t>96578</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>126704</t>
+          <t>128310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>173968</t>
+          <t>174334</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>207679</t>
+          <t>208270</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278940</t>
+          <t>278221</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327811</t>
+          <t>327741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>166045</t>
+          <t>167003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208101</t>
+          <t>208167</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>238288</t>
+          <t>239283</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>280786</t>
+          <t>278758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>416501</t>
+          <t>413359</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472385</t>
+          <t>472055</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108752</t>
+          <t>109731</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>146596</t>
+          <t>144858</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>123627</t>
+          <t>122155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>159528</t>
+          <t>160430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>240356</t>
+          <t>243693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>292935</t>
+          <t>297132</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,62%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17312</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40297</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24361</t>
+          <t>24168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51538</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>47498</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81100</t>
+          <t>80594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62182</t>
+          <t>59838</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112823</t>
+          <t>110405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67703</t>
+          <t>65150</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117414</t>
+          <t>116974</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>144946</t>
+          <t>145332</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214493</t>
+          <t>215466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165271</t>
+          <t>159559</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>273291</t>
+          <t>277033</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184131</t>
+          <t>184715</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>299828</t>
+          <t>302841</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394645</t>
+          <t>394505</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>554771</t>
+          <t>555970</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>690700</t>
+          <t>708418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1121811</t>
+          <t>1125452</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1006778</t>
+          <t>1006255</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1451524</t>
+          <t>1437370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2137093</t>
+          <t>2137094</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1830117</t>
+          <t>1802211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2467852</t>
+          <t>2435691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>53,84%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>779591</t>
+          <t>776702</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1359481</t>
+          <t>1349282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,4%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>514633</t>
+          <t>536948</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>831961</t>
+          <t>847358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1398312</t>
+          <t>1407459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2111403</t>
+          <t>2151919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,56%</t>
         </is>
       </c>
     </row>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524339</t>
+          <t>4524340</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524339</t>
+          <t>4524340</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524339</t>
+          <t>4524340</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20941</t>
+          <t>20495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2300</t>
+          <t>2604</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8863</t>
+          <t>9218</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25470</t>
+          <t>28270</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,16%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>7648</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12717</t>
+          <t>12338</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27593</t>
+          <t>27474</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23596</t>
+          <t>23519</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>46372</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46922</t>
+          <t>47393</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>76828</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>55048</t>
+          <t>54815</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>83047</t>
+          <t>84313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>107294</t>
+          <t>108534</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>148606</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>270558</t>
+          <t>272258</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>325522</t>
+          <t>328025</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,34%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>291476</t>
+          <t>289280</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335125</t>
+          <t>335213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>577093</t>
+          <t>574169</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>648324</t>
+          <t>647868</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,57%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235633</t>
+          <t>235953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295436</t>
+          <t>293233</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234361</t>
+          <t>232802</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276010</t>
+          <t>278998</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481706</t>
+          <t>481018</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>553863</t>
+          <t>556411</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,57%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49535</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83677</t>
+          <t>84122</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>67032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100304</t>
+          <t>100827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>124755</t>
+          <t>122030</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176502</t>
+          <t>176583</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>127726</t>
+          <t>129099</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192837</t>
+          <t>192460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185290</t>
+          <t>185576</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>256872</t>
+          <t>255616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>336081</t>
+          <t>334585</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>438645</t>
+          <t>436365</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>315759</t>
+          <t>314219</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>455627</t>
+          <t>455808</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424369</t>
+          <t>424357</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>570234</t>
+          <t>575652</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>797161</t>
+          <t>788384</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1001697</t>
+          <t>1001946</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,7 +3087,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1158356</t>
+          <t>1152068</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1604385</t>
+          <t>1601830</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1576909</t>
+          <t>1578202</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2051110</t>
+          <t>2106339</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2868867</t>
+          <t>2864563</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3525977</t>
+          <t>3504821</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1161058</t>
+          <t>1164322</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1822191</t>
+          <t>1807957</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>914841</t>
+          <t>915191</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1242136</t>
+          <t>1240455</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2178152</t>
+          <t>2199153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2960700</t>
+          <t>3032128</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57C1_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57C1_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27281</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19075</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37796</t>
+          <t>44433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42731</t>
+          <t>44946</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34353</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>55630</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70012</t>
+          <t>76295</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58485</t>
+          <t>63344</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86342</t>
+          <t>92412</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60314</t>
+          <t>63258</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48494</t>
+          <t>51531</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>77584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>114846</t>
+          <t>126487</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100529</t>
+          <t>111573</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>130481</t>
+          <t>143200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>175160</t>
+          <t>189745</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>154743</t>
+          <t>169374</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>195147</t>
+          <t>210852</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>111602</t>
+          <t>125053</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>96578</t>
+          <t>109013</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>128310</t>
+          <t>144125</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>191197</t>
+          <t>210995</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>174334</t>
+          <t>192389</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>208270</t>
+          <t>231089</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>302799</t>
+          <t>336048</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>278221</t>
+          <t>309791</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>327741</t>
+          <t>361837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,09%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>186185</t>
+          <t>204593</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>167003</t>
+          <t>182914</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>208167</t>
+          <t>226072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>258202</t>
+          <t>283963</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>239283</t>
+          <t>263940</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>278758</t>
+          <t>305859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>444387</t>
+          <t>488556</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>413359</t>
+          <t>458907</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>472055</t>
+          <t>519737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,48%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>125895</t>
+          <t>150413</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109731</t>
+          <t>130432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>144858</t>
+          <t>174174</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>139592</t>
+          <t>145657</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122155</t>
+          <t>128052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160430</t>
+          <t>164391</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>265487</t>
+          <t>296070</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243693</t>
+          <t>267631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>297132</t>
+          <t>326044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,51%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>511277</t>
+          <t>574666</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>511277</t>
+          <t>574666</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>511277</t>
+          <t>574666</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>746569</t>
+          <t>812048</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>746569</t>
+          <t>812048</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>746569</t>
+          <t>812048</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1257846</t>
+          <t>1386713</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1257846</t>
+          <t>1386713</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1257846</t>
+          <t>1386713</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27389</t>
+          <t>29665</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39397</t>
+          <t>42175</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>35670</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24168</t>
+          <t>27970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>54111</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>63058</t>
+          <t>68283</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47498</t>
+          <t>53879</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80594</t>
+          <t>87942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>90343</t>
+          <t>96004</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59838</t>
+          <t>79960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>110405</t>
+          <t>119373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92405</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65150</t>
+          <t>89128</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116974</t>
+          <t>126368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>182747</t>
+          <t>201448</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>145332</t>
+          <t>178133</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215466</t>
+          <t>227497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>231578</t>
+          <t>249865</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159559</t>
+          <t>221811</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>277033</t>
+          <t>282645</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>258922</t>
+          <t>290256</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184715</t>
+          <t>263421</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>302841</t>
+          <t>321150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>490500</t>
+          <t>540121</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>394505</t>
+          <t>495550</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>555970</t>
+          <t>580845</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>983066</t>
+          <t>1057635</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>708418</t>
+          <t>1007933</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1125452</t>
+          <t>1111133</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1154028</t>
+          <t>1025531</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1006255</t>
+          <t>981258</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1437370</t>
+          <t>1068911</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2137094</t>
+          <t>2083167</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1802211</t>
+          <t>2011150</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2435691</t>
+          <t>2152320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>956314</t>
+          <t>795853</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>776702</t>
+          <t>746464</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1349282</t>
+          <t>848912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>694626</t>
+          <t>707802</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>536948</t>
+          <t>665762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>847358</t>
+          <t>748450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1650940</t>
+          <t>1503655</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1407459</t>
+          <t>1438020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2151919</t>
+          <t>1575268</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2288690</t>
+          <t>2229022</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2288690</t>
+          <t>2229022</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2288690</t>
+          <t>2229022</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2235650</t>
+          <t>2167652</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2235650</t>
+          <t>2167652</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2235650</t>
+          <t>2167652</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>4524340</t>
+          <t>4396674</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4524340</t>
+          <t>4396674</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4524340</t>
+          <t>4396674</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11323</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4630</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20495</t>
+          <t>21543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>6466</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10858</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>15772</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>11115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28270</t>
+          <t>29246</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14613</t>
+          <t>15191</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7648</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26104</t>
+          <t>26933</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18643</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27474</t>
+          <t>27208</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>34500</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23519</t>
+          <t>24769</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>46372</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2315,22 +2315,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60058</t>
+          <t>66398</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76828</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2340,7 +2340,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,67 +2350,67 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68012</t>
+          <t>74215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>54815</t>
+          <t>59746</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>84313</t>
+          <t>91203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>8,13%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>12,41%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>140613</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>120067</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>167563</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>8,3%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>12,77%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>128070</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>108534</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>148606</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>9,8%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>299045</t>
+          <t>328277</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>272258</t>
+          <t>300587</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>328025</t>
+          <t>359001</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>46,25%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>312832</t>
+          <t>343308</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>289280</t>
+          <t>317701</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>335213</t>
+          <t>367607</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>611877</t>
+          <t>671584</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>574169</t>
+          <t>636125</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>647868</t>
+          <t>708956</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>49,01%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>262303</t>
+          <t>290399</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>235953</t>
+          <t>263111</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>293233</t>
+          <t>319692</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>255808</t>
+          <t>291579</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232802</t>
+          <t>266824</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>278998</t>
+          <t>314050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,68%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>518112</t>
+          <t>581978</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>481018</t>
+          <t>544264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>556411</t>
+          <t>617913</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>42,72%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>65273</t>
+          <t>72336</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>57795</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>84122</t>
+          <t>93047</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>83569</t>
+          <t>90032</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67032</t>
+          <t>74941</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100827</t>
+          <t>107971</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>148842</t>
+          <t>162368</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>122030</t>
+          <t>141785</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>176583</t>
+          <t>188296</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>165270</t>
+          <t>174453</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>129099</t>
+          <t>150580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>192460</t>
+          <t>201384</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>225894</t>
+          <t>251239</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>185576</t>
+          <t>228198</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>255616</t>
+          <t>280677</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>391163</t>
+          <t>425692</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>334585</t>
+          <t>389976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>436365</t>
+          <t>465019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>403238</t>
+          <t>441316</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>314219</t>
+          <t>402170</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>455808</t>
+          <t>484552</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>518131</t>
+          <t>575466</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>424357</t>
+          <t>538679</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>575652</t>
+          <t>613085</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>921369</t>
+          <t>1016782</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>788384</t>
+          <t>965523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1001946</t>
+          <t>1070603</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1468296</t>
+          <t>1590505</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1152068</t>
+          <t>1525342</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1601830</t>
+          <t>1654699</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>45,25%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1725061</t>
+          <t>1652802</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1578202</t>
+          <t>1603833</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2106339</t>
+          <t>1707851</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3193357</t>
+          <t>3243307</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2864563</t>
+          <t>3160573</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3504821</t>
+          <t>3324401</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>45,04%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1344513</t>
+          <t>1236665</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1164322</t>
+          <t>1169152</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1807957</t>
+          <t>1303395</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>35,18%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1090026</t>
+          <t>1145038</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>915191</t>
+          <t>1090707</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1240455</t>
+          <t>1196216</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2434539</t>
+          <t>2381703</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2199153</t>
+          <t>2299275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3032128</t>
+          <t>2466595</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>34,12%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3446590</t>
+          <t>3515275</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3446590</t>
+          <t>3515275</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3446590</t>
+          <t>3515275</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3642681</t>
+          <t>3714577</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3642681</t>
+          <t>3714577</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3642681</t>
+          <t>3714577</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7089271</t>
+          <t>7229852</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7089271</t>
+          <t>7229852</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7089271</t>
+          <t>7229852</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
